--- a/templates/MAS_Nakit_Radar_Standart_Import_v2.xlsx
+++ b/templates/MAS_Nakit_Radar_Standart_Import_v2.xlsx
@@ -1100,7 +1100,7 @@
     <comment ref="Q1" authorId="0">
       <text>
         <r>
-          <t>active / closed / restructured.</t>
+          <t>active / closed / planned.</t>
         </r>
       </text>
     </comment>
@@ -1241,7 +1241,7 @@
       <text>
         <r>
           <t xml:space="preserve">ZORUNLU ALAN
-ZORUNLU. opening_balance = ayın devri (ay başı bakiye). Diğerleri gelir/gider kalemleridir. Kasa = devir + gelir − gider olarak SİSTEM hesaplar; siz kapanış yazmazsınız.</t>
+ZORUNLU. Bu satırın ne olduğu: müşteri tahsilatı, tedarikçi ödemesi, vergi, kredi ödemesi… DEVİR BURAYA YAZILMAZ — ay başı bakiye bir satır tipi değil, ayın kendi alanıdır. Kasa = devir + gelir − gider olarak SİSTEM hesaplar; siz kapanış yazmazsınız.</t>
         </r>
       </text>
     </comment>
@@ -9782,11 +9782,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="E2:E500">
       <formula1>"TRY,USD,EUR,GBP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: active, closed, restructured" sqref="Q10:Q500">
-      <formula1>"active,closed,restructured"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: active, closed, planned" sqref="Q10:Q500">
+      <formula1>"active,closed,planned"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: active, closed, restructured" sqref="Q2:Q500">
-      <formula1>"active,closed,restructured"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: active, closed, planned" sqref="Q2:Q500">
+      <formula1>"active,closed,planned"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10915,11 +10915,11 @@
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: opening_balance, customer_income, vendor_payment, operational_cost, tax, bank_balance, credit_card, adjustment, loan_payment, other" sqref="D10:D500">
-      <formula1>"opening_balance,customer_income,vendor_payment,operational_cost,tax,bank_balance,credit_card,adjustment,loan_payment,other"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: customer_income, vendor_payment, bank_balance, credit_card, loan_payment, check_payment, operational_cost, tax, transfer, adjustment" sqref="D10:D500">
+      <formula1>"customer_income,vendor_payment,bank_balance,credit_card,loan_payment,check_payment,operational_cost,tax,transfer,adjustment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: opening_balance, customer_income, vendor_payment, operational_cost, tax, bank_balance, credit_card, adjustment, loan_payment, other" sqref="D2:D500">
-      <formula1>"opening_balance,customer_income,vendor_payment,operational_cost,tax,bank_balance,credit_card,adjustment,loan_payment,other"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: customer_income, vendor_payment, bank_balance, credit_card, loan_payment, check_payment, operational_cost, tax, transfer, adjustment" sqref="D2:D500">
+      <formula1>"customer_income,vendor_payment,bank_balance,credit_card,loan_payment,check_payment,operational_cost,tax,transfer,adjustment"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: inflow, outflow, balance" sqref="H10:H500">
       <formula1>"inflow,outflow,balance"</formula1>

--- a/templates/MAS_Nakit_Radar_Standart_Import_v2.xlsx
+++ b/templates/MAS_Nakit_Radar_Standart_Import_v2.xlsx
@@ -342,7 +342,7 @@
       <text>
         <r>
           <t xml:space="preserve">ZORUNLU ALAN
-ZORUNLU. inflow / outflow.</t>
+ZORUNLU. income (gelir) / expense (gider).</t>
         </r>
       </text>
     </comment>
@@ -411,7 +411,7 @@
       <text>
         <r>
           <t xml:space="preserve">ZORUNLU ALAN
-TRY, USD, EUR veya GBP. Boş bırakılırsa TRY varsayılmaz — eksik kabul edilir ve incelemeye düşer.</t>
+ZORUNLU. USD, EUR veya GBP. TRY bir döviz pozisyonu değildir.</t>
         </r>
       </text>
     </comment>
@@ -419,7 +419,7 @@
       <text>
         <r>
           <t xml:space="preserve">ZORUNLU ALAN
-ZORUNLU. asset / liability / receivable / payable / hedge.</t>
+ZORUNLU. bank_balance / receivable (alacak) / payable (borç) / loan / facility (tahsis) / forward / other.</t>
         </r>
       </text>
     </comment>
@@ -1182,7 +1182,7 @@
     <comment ref="H1" authorId="0">
       <text>
         <r>
-          <t>planned / paid / overdue / cancelled.</t>
+          <t>planned / unpaid / partial / paid / late (geciken) / cancelled.</t>
         </r>
       </text>
     </comment>
@@ -1365,7 +1365,7 @@
     <comment ref="G1" authorId="0">
       <text>
         <r>
-          <t>vadesiz / vadeli / kredi / pos / diger.</t>
+          <t>bank_account (vadesiz/vadeli banka hesabı) / credit_card / loan / check_account / cash / other.</t>
         </r>
       </text>
     </comment>
@@ -1608,7 +1608,7 @@
     <comment ref="K1" authorId="0">
       <text>
         <r>
-          <t>draft / issued / paid / partial / cancelled.</t>
+          <t>draft / open (kesildi, tahsilat bekliyor) / partial / paid / closed / cancelled.</t>
         </r>
       </text>
     </comment>
@@ -5416,11 +5416,11 @@
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: inflow, outflow" sqref="E10:E500">
-      <formula1>"inflow,outflow"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: income, expense" sqref="E10:E500">
+      <formula1>"income,expense"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: inflow, outflow" sqref="E2:E500">
-      <formula1>"inflow,outflow"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: income, expense" sqref="E2:E500">
+      <formula1>"income,expense"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="G10:G500">
       <formula1>"TRY,USD,EUR,GBP"</formula1>
@@ -5992,17 +5992,17 @@
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="C10:C500">
-      <formula1>"TRY,USD,EUR,GBP"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: USD, EUR, GBP" sqref="C10:C500">
+      <formula1>"USD,EUR,GBP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="C2:C500">
-      <formula1>"TRY,USD,EUR,GBP"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: USD, EUR, GBP" sqref="C2:C500">
+      <formula1>"USD,EUR,GBP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: asset, liability, receivable, payable, hedge" sqref="D10:D500">
-      <formula1>"asset,liability,receivable,payable,hedge"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: bank_balance, receivable, payable, loan, facility, forward, other" sqref="D10:D500">
+      <formula1>"bank_balance,receivable,payable,loan,facility,forward,other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: asset, liability, receivable, payable, hedge" sqref="D2:D500">
-      <formula1>"asset,liability,receivable,payable,hedge"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: bank_balance, receivable, payable, loan, facility, forward, other" sqref="D2:D500">
+      <formula1>"bank_balance,receivable,payable,loan,facility,forward,other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10343,11 +10343,11 @@
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: planned, paid, overdue, cancelled" sqref="H10:H500">
-      <formula1>"planned,paid,overdue,cancelled"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: planned, unpaid, partial, paid, late" sqref="H10:H500">
+      <formula1>"planned,unpaid,partial,paid,late"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: planned, paid, overdue, cancelled" sqref="H2:H500">
-      <formula1>"planned,paid,overdue,cancelled"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: planned, unpaid, partial, paid, late" sqref="H2:H500">
+      <formula1>"planned,unpaid,partial,paid,late"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11514,11 +11514,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="F2:F500">
       <formula1>"TRY,USD,EUR,GBP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: vadesiz, vadeli, kredi, pos, diger" sqref="G10:G500">
-      <formula1>"vadesiz,vadeli,kredi,pos,diger"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: bank_account, credit_card, loan, check_account, cash, other" sqref="G10:G500">
+      <formula1>"bank_account,credit_card,loan,check_account,cash,other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: vadesiz, vadeli, kredi, pos, diger" sqref="G2:G500">
-      <formula1>"vadesiz,vadeli,kredi,pos,diger"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: bank_account, credit_card, loan, check_account, cash, other" sqref="G2:G500">
+      <formula1>"bank_account,credit_card,loan,check_account,cash,other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12675,11 +12675,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="J2:J500">
       <formula1>"TRY,USD,EUR,GBP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: draft, issued, paid, partial, cancelled" sqref="K10:K500">
-      <formula1>"draft,issued,paid,partial,cancelled"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: draft, open, partial, paid" sqref="K10:K500">
+      <formula1>"draft,open,partial,paid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: draft, issued, paid, partial, cancelled" sqref="K2:K500">
-      <formula1>"draft,issued,paid,partial,cancelled"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: draft, open, partial, paid" sqref="K2:K500">
+      <formula1>"draft,open,partial,paid"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/MAS_Nakit_Radar_Standart_Import_v2.xlsx
+++ b/templates/MAS_Nakit_Radar_Standart_Import_v2.xlsx
@@ -948,7 +948,7 @@
       <text>
         <r>
           <t xml:space="preserve">ZORUNLU ALAN
-TRY, USD, EUR veya GBP. Boş bırakılırsa TRY varsayılmaz — eksik kabul edilir ve incelemeye düşer.</t>
+V2.0'da bu sayfa yalnız TRY kayıtlarını finans tablolarına aktarır. Başka para birimli satırlar kaynakta KORUNUR ve incelemeye düşer, ama çek/kredi toplamlarına karışmaz — çünkü bu sürüm karışık para birimlerini güvenle toplayamaz.</t>
         </r>
       </text>
     </comment>
@@ -1015,7 +1015,7 @@
       <text>
         <r>
           <t xml:space="preserve">ZORUNLU ALAN
-TRY, USD, EUR veya GBP. Boş bırakılırsa TRY varsayılmaz — eksik kabul edilir ve incelemeye düşer.</t>
+V2.0'da bu sayfa yalnız TRY kayıtlarını finans tablolarına aktarır. Başka para birimli satırlar kaynakta KORUNUR ve incelemeye düşer, ama çek/kredi toplamlarına karışmaz — çünkü bu sürüm karışık para birimlerini güvenle toplayamaz.</t>
         </r>
       </text>
     </comment>
@@ -9178,11 +9178,11 @@
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="H10:H500">
-      <formula1>"TRY,USD,EUR,GBP"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY" sqref="H10:H500">
+      <formula1>"TRY"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="H2:H500">
-      <formula1>"TRY,USD,EUR,GBP"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY" sqref="H2:H500">
+      <formula1>"TRY"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: planned, cleared, bounced, cancelled" sqref="I10:I500">
       <formula1>"planned,cleared,bounced,cancelled"</formula1>
@@ -9776,11 +9776,11 @@
   </sheetData>
   <autoFilter ref="A1:R1"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="E10:E500">
-      <formula1>"TRY,USD,EUR,GBP"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY" sqref="E10:E500">
+      <formula1>"TRY"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY, USD, EUR, GBP" sqref="E2:E500">
-      <formula1>"TRY,USD,EUR,GBP"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: TRY" sqref="E2:E500">
+      <formula1>"TRY"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Geçersiz değer" error="İzin verilen değerler: active, closed, planned" sqref="Q10:Q500">
       <formula1>"active,closed,planned"</formula1>
